--- a/抖音账号运营模板包/05_数据记录/账号数据汇总.xlsx
+++ b/抖音账号运营模板包/05_数据记录/账号数据汇总.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -64,12 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -555,7 +560,6 @@
           <t>B+</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,7 +608,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -653,7 +656,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -702,7 +704,56 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>第27期</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>应届生选offer：工资还是发展</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2376</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>38.48%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -800,7 +851,6 @@
           <t>≥3%</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -818,7 +868,6 @@
           <t>≥1%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -836,7 +885,6 @@
           <t>≥1%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -907,7 +955,6 @@
           <t>待拍摄</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -930,7 +977,6 @@
           <t>待拍摄</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -953,7 +999,6 @@
           <t>待拍摄</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -976,7 +1021,6 @@
           <t>待拍摄</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -999,7 +1043,6 @@
           <t>待拍摄</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
